--- a/output/pdf_financials_xlsx/RV.xlsx
+++ b/output/pdf_financials_xlsx/RV.xlsx
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.044366</v>
+        <v>-0.044366</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.256234</v>
+        <v>-0.256234</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.666633</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.044366</v>
+        <v>-0.044366</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.256234</v>
+        <v>-0.256234</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.667633</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.044366</v>
+        <v>-0.044366</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.256234</v>
+        <v>-0.256234</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.667633</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-12.8117</v>
+        <v>12.8117</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>6.67633</v>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.044366</v>
+        <v>-0.044366</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.256234</v>
+        <v>-0.256234</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.666633</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.044366</v>
+        <v>-0.044366</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.256234</v>
+        <v>-0.256234</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.666633</v>
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0.1500075753825568</v>
@@ -3310,25 +3310,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.229159</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.105595</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.953527</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.969201</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.028856</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.114105</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.114105</v>
       </c>
     </row>
     <row r="93">
@@ -5996,7 +5996,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -6812,7 +6816,11 @@
           <t>Reserves 18</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -7586,7 +7594,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -8348,7 +8360,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -9496,7 +9512,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -9990,7 +10010,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -27070,10 +27094,10 @@
         </is>
       </c>
       <c r="G407" s="5" t="n">
-        <v>0.115957</v>
+        <v>-0.115957</v>
       </c>
       <c r="H407" s="5" t="n">
-        <v>0.118343</v>
+        <v>-0.118343</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -27446,13 +27470,13 @@
         </is>
       </c>
       <c r="E414" s="5" t="n">
-        <v>0.044366</v>
+        <v>-0.044366</v>
       </c>
       <c r="F414" s="5" t="n">
-        <v>0.256234</v>
+        <v>-0.256234</v>
       </c>
       <c r="G414" s="5" t="n">
-        <v>0.115957</v>
+        <v>-0.115957</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RV.xlsx
+++ b/output/pdf_financials_xlsx/RV.xlsx
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008739</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022256</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032677</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>-0.044366</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.256234</v>
+        <v>-0.247495</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.666633</v>
+        <v>-0.644377</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.464822</v>
+        <v>-3.432145</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.255274</v>
@@ -1323,13 +1323,13 @@
         <v>-0.044366</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.256234</v>
+        <v>-0.247495</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.666633</v>
+        <v>-0.644377</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.464822</v>
+        <v>-3.432145</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.255274</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-611.9492178894029</v>
+        <v>-591.5188734669898</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-140.707602702537</v>
+        <v>-139.3805785917714</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-66.90464620790192</v>
@@ -1471,16 +1471,16 @@
         <v>2.092893</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.982482</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.4561</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.8261230000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.229719</v>
       </c>
     </row>
     <row r="35">
@@ -1533,16 +1533,16 @@
         <v>2.092893</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.982482</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.4561</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.8261230000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.229719</v>
       </c>
     </row>
     <row r="37">
@@ -1905,16 +1905,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.01139</v>
+        <v>0.028908</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.838036</v>
+        <v>0.381936</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.090889</v>
+        <v>0.264766</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.349492</v>
+        <v>0.119773</v>
       </c>
     </row>
     <row r="49">
@@ -4281,22 +4281,22 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008333</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.129951</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.14015</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.14015</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.120969</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.109652</v>
       </c>
     </row>
     <row r="125">
@@ -4312,22 +4312,22 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008333</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.129951</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.14015</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.14015</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.120969</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.109652</v>
       </c>
     </row>
     <row r="126">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11462,7 +11462,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -19546,7 +19550,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -24400,7 +24408,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -25128,7 +25136,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -26914,7 +26922,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">

--- a/output/pdf_financials_xlsx/RV.xlsx
+++ b/output/pdf_financials_xlsx/RV.xlsx
@@ -3918,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -10868,7 +10868,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RV.xlsx
+++ b/output/pdf_financials_xlsx/RV.xlsx
@@ -923,7 +923,7 @@
         <v>0.001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.09493500000000001</v>
+        <v>-0.09493500000000001</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -2427,22 +2427,22 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.643201</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.1564</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.178276</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.252126</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.392965</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.595603</v>
       </c>
     </row>
     <row r="65">
@@ -2520,22 +2520,22 @@
         <v>0.005765</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.113474</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.060284</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.154396</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.201183</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.26349</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.301373</v>
       </c>
     </row>
     <row r="68">
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.008264000000000001</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.071119</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.430345</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.245575</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.072669</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.011897</v>
       </c>
     </row>
     <row r="111">
@@ -10122,7 +10122,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -11090,7 +11094,11 @@
           <t>Proceeds from shares issued in private placement</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -13008,7 +13016,11 @@
           <t>Proceeds from units issued in private placement</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -14070,7 +14082,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -15462,7 +15478,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -15850,7 +15870,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -17536,7 +17560,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -18038,7 +18066,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -21122,7 +21154,11 @@
           <t>Proceeds from share issuance, net 6</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -25700,7 +25736,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -26382,7 +26422,11 @@
           <t>Deferred income tax recovery 13,17</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
